--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Mistral-7B-Instruct-v0.3/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E3">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H3">
         <v>426</v>
